--- a/output/graficos_nacionales/plot_nacional_migracion_sexo_2022_nacional.xlsx
+++ b/output/graficos_nacionales/plot_nacional_migracion_sexo_2022_nacional.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:10</t>
+    <t xml:space="preserve">2026-09-29 19:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_migracion_sexo_2022_nacional.xlsx
+++ b/output/graficos_nacionales/plot_nacional_migracion_sexo_2022_nacional.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 19:00</t>
+    <t xml:space="preserve">2026-10-01 00:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_migracion_sexo_2022_nacional.xlsx
+++ b/output/graficos_nacionales/plot_nacional_migracion_sexo_2022_nacional.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 00:55</t>
+    <t xml:space="preserve">2026-10-01 19:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_migracion_sexo_2022_nacional.xlsx
+++ b/output/graficos_nacionales/plot_nacional_migracion_sexo_2022_nacional.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:15</t>
+    <t xml:space="preserve">2026-10-05 04:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
